--- a/Assets/_ProtoType_Merge/ASB/Data/Excel/H.I 베타 전투 밸런스 데이터 테이블.xlsx
+++ b/Assets/_ProtoType_Merge/ASB/Data/Excel/H.I 베타 전투 밸런스 데이터 테이블.xlsx
@@ -3,14 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k2104200016\Downloads\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9D31F93-404F-4A17-864A-9E4E5FA7C23C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="834" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" tabRatio="834" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="수정 내역" sheetId="41" r:id="rId1"/>
@@ -23,8 +17,8 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" chartTrackingRefBase="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -3126,7 +3120,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.34998626667073579"/>
+        <fgColor theme="0" tint="-0.349986266670736"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3170,7 +3164,7 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3407,20 +3401,21 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="표준 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="표준 3" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="표준 2" xfId="1" builtinId="0"/>
+    <cellStyle name="표준 3" xfId="2" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -4982,7 +4977,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{716AB573-FB99-421B-B82D-80DF2560487A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:AM20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="17"/>
   <cols>
@@ -5010,7 +5005,6 @@
     <col min="36" max="36" width="25.1640625" style="29" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="17.58203125" style="29" bestFit="1" customWidth="1"/>
     <col min="38" max="65" width="15.58203125" style="29" customWidth="1"/>
-    <col min="66" max="16384" width="9" style="29"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39">
@@ -5297,14 +5291,14 @@
       <c r="G6" s="66">
         <v>5</v>
       </c>
-      <c r="H6" s="68">
-        <v>0.10000000149011599</v>
-      </c>
-      <c r="I6" s="68">
-        <v>0.10000000149011599</v>
-      </c>
-      <c r="J6" s="68">
-        <v>0.10000000149011599</v>
+      <c r="H6" s="80">
+        <v>0.100000001490116</v>
+      </c>
+      <c r="I6" s="80">
+        <v>0.100000001490116</v>
+      </c>
+      <c r="J6" s="80">
+        <v>0.100000001490116</v>
       </c>
       <c r="K6" s="66">
         <v>2</v>
@@ -5328,25 +5322,49 @@
         <v>0</v>
       </c>
       <c r="R6" s="66"/>
-      <c r="S6" s="66"/>
-      <c r="T6" s="66"/>
-      <c r="U6" s="68">
-        <v>1</v>
-      </c>
-      <c r="V6" s="68">
-        <v>0</v>
-      </c>
-      <c r="W6" s="66"/>
-      <c r="X6" s="69"/>
-      <c r="Y6" s="66"/>
-      <c r="Z6" s="66"/>
-      <c r="AA6" s="66"/>
-      <c r="AB6" s="66"/>
+      <c r="S6" s="66">
+        <v>0</v>
+      </c>
+      <c r="T6" s="66">
+        <v>0</v>
+      </c>
+      <c r="U6" s="80">
+        <v>1</v>
+      </c>
+      <c r="V6" s="80">
+        <v>0</v>
+      </c>
+      <c r="W6" s="66" t="s">
+        <v>455</v>
+      </c>
+      <c r="X6" s="69" t="s">
+        <v>455</v>
+      </c>
+      <c r="Y6" s="66">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="66">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="66">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="66">
+        <v>0</v>
+      </c>
       <c r="AC6" s="66"/>
-      <c r="AD6" s="66"/>
-      <c r="AE6" s="66"/>
-      <c r="AF6" s="68"/>
-      <c r="AG6" s="68"/>
+      <c r="AD6" s="66">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="66">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="80">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="80">
+        <v>0</v>
+      </c>
       <c r="AH6" s="3" t="s">
         <v>477</v>
       </c>
@@ -5385,13 +5403,13 @@
       <c r="G7" s="66">
         <v>6</v>
       </c>
-      <c r="H7" s="68">
-        <v>0.10000000149011599</v>
-      </c>
-      <c r="I7" s="68">
-        <v>0.10000000149011599</v>
-      </c>
-      <c r="J7" s="68">
+      <c r="H7" s="80">
+        <v>0.100000001490116</v>
+      </c>
+      <c r="I7" s="80">
+        <v>0.100000001490116</v>
+      </c>
+      <c r="J7" s="80">
         <v>0.25</v>
       </c>
       <c r="K7" s="66">
@@ -5422,10 +5440,10 @@
       <c r="T7" s="66">
         <v>0</v>
       </c>
-      <c r="U7" s="68">
-        <v>1</v>
-      </c>
-      <c r="V7" s="68">
+      <c r="U7" s="80">
+        <v>1</v>
+      </c>
+      <c r="V7" s="80">
         <v>0</v>
       </c>
       <c r="W7" s="66" t="s">
@@ -5447,16 +5465,18 @@
         <v>1</v>
       </c>
       <c r="AC7" s="66" t="s">
-        <v>480</v>
+        <v>130</v>
       </c>
       <c r="AD7" s="66">
         <v>0</v>
       </c>
-      <c r="AE7" s="66"/>
-      <c r="AF7" s="68">
-        <v>0.6</v>
-      </c>
-      <c r="AG7" s="68">
+      <c r="AE7" s="66">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="80">
+        <v>0.600000023841858</v>
+      </c>
+      <c r="AG7" s="80">
         <v>0</v>
       </c>
       <c r="AH7" s="3" t="s">
@@ -5497,14 +5517,14 @@
       <c r="G8" s="66">
         <v>8</v>
       </c>
-      <c r="H8" s="68">
-        <v>0.10000000149011599</v>
-      </c>
-      <c r="I8" s="68">
+      <c r="H8" s="80">
+        <v>0.100000001490116</v>
+      </c>
+      <c r="I8" s="80">
         <v>0.25</v>
       </c>
-      <c r="J8" s="68">
-        <v>0.10000000149011599</v>
+      <c r="J8" s="80">
+        <v>0.100000001490116</v>
       </c>
       <c r="K8" s="66">
         <v>0</v>
@@ -5534,10 +5554,10 @@
       <c r="T8" s="66">
         <v>0</v>
       </c>
-      <c r="U8" s="68">
-        <v>0.80000001192092896</v>
-      </c>
-      <c r="V8" s="68">
+      <c r="U8" s="80">
+        <v>0.800000011920929</v>
+      </c>
+      <c r="V8" s="80">
         <v>0</v>
       </c>
       <c r="W8" s="66" t="s">
@@ -5565,10 +5585,10 @@
       <c r="AE8" s="66">
         <v>0</v>
       </c>
-      <c r="AF8" s="68">
-        <v>0</v>
-      </c>
-      <c r="AG8" s="68">
+      <c r="AF8" s="80">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="80">
         <v>0</v>
       </c>
       <c r="AH8" s="3" t="s">
@@ -5609,14 +5629,14 @@
       <c r="G9" s="70">
         <v>6</v>
       </c>
-      <c r="H9" s="71">
-        <v>0.20000000298023199</v>
-      </c>
-      <c r="I9" s="71">
-        <v>0.15000000596046401</v>
-      </c>
-      <c r="J9" s="71">
-        <v>0.15000000596046401</v>
+      <c r="H9" s="80">
+        <v>0.200000002980232</v>
+      </c>
+      <c r="I9" s="80">
+        <v>0.150000005960464</v>
+      </c>
+      <c r="J9" s="80">
+        <v>0.150000005960464</v>
       </c>
       <c r="K9" s="70">
         <v>2</v>
@@ -5648,10 +5668,10 @@
       <c r="T9" s="70">
         <v>0</v>
       </c>
-      <c r="U9" s="71">
+      <c r="U9" s="80">
         <v>1.20000004768372</v>
       </c>
-      <c r="V9" s="71">
+      <c r="V9" s="80">
         <v>1</v>
       </c>
       <c r="W9" s="70" t="s">
@@ -5679,10 +5699,10 @@
       <c r="AE9" s="70">
         <v>0</v>
       </c>
-      <c r="AF9" s="71">
-        <v>0</v>
-      </c>
-      <c r="AG9" s="71">
+      <c r="AF9" s="80">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="80">
         <v>0</v>
       </c>
       <c r="AH9" s="47" t="s">
@@ -5723,17 +5743,17 @@
       <c r="G10" s="66">
         <v>6</v>
       </c>
-      <c r="H10" s="68">
+      <c r="H10" s="80">
         <v>0.25</v>
       </c>
-      <c r="I10" s="68">
-        <v>0.20000000298023199</v>
-      </c>
-      <c r="J10" s="68">
-        <v>0.20000000298023199</v>
+      <c r="I10" s="80">
+        <v>0.200000002980232</v>
+      </c>
+      <c r="J10" s="80">
+        <v>0.200000002980232</v>
       </c>
       <c r="K10" s="66">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L10" s="66" t="s">
         <v>484</v>
@@ -5760,10 +5780,10 @@
       <c r="T10" s="66">
         <v>0</v>
       </c>
-      <c r="U10" s="68">
-        <v>1</v>
-      </c>
-      <c r="V10" s="68">
+      <c r="U10" s="80">
+        <v>1</v>
+      </c>
+      <c r="V10" s="80">
         <v>0</v>
       </c>
       <c r="W10" s="66" t="s">
@@ -5793,11 +5813,11 @@
       <c r="AE10" s="66">
         <v>1</v>
       </c>
-      <c r="AF10" s="68">
-        <v>1</v>
-      </c>
-      <c r="AG10" s="68">
-        <v>0.8</v>
+      <c r="AF10" s="80">
+        <v>1</v>
+      </c>
+      <c r="AG10" s="80">
+        <v>0.800000011920929</v>
       </c>
       <c r="AH10" s="3" t="s">
         <v>487</v>
@@ -5812,7 +5832,7 @@
         <v>10</v>
       </c>
       <c r="AL10" s="43">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AM10" s="43">
         <v>3</v>

--- a/Assets/_ProtoType_Merge/ASB/Data/Excel/H.I 베타 전투 밸런스 데이터 테이블.xlsx
+++ b/Assets/_ProtoType_Merge/ASB/Data/Excel/H.I 베타 전투 밸런스 데이터 테이블.xlsx
@@ -3,14 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7615BFD-E49B-4DA8-93B7-038A59603D39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="801" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="801" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="수정 내역" sheetId="41" r:id="rId1"/>
@@ -23,11 +17,11 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
+    <ext uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures">
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
@@ -3305,7 +3299,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.34998626667073579"/>
+        <fgColor theme="0" tint="-0.349986266670736"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3349,7 +3343,7 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3493,20 +3487,22 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="표준 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="표준 3" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="표준 2" xfId="1" builtinId="0"/>
+    <cellStyle name="표준 3" xfId="2" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -4846,7 +4842,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{716AB573-FB99-421B-B82D-80DF2560487A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:AM13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
@@ -5160,14 +5156,14 @@
       <c r="G6" s="36">
         <v>5</v>
       </c>
-      <c r="H6" s="38">
-        <v>0.10000000149011599</v>
-      </c>
-      <c r="I6" s="38">
-        <v>0.10000000149011599</v>
-      </c>
-      <c r="J6" s="38">
-        <v>0.10000000149011599</v>
+      <c r="H6" s="50">
+        <v>0.100000001490116</v>
+      </c>
+      <c r="I6" s="50">
+        <v>0.100000001490116</v>
+      </c>
+      <c r="J6" s="50">
+        <v>0.100000001490116</v>
       </c>
       <c r="K6" s="36">
         <v>2</v>
@@ -5191,25 +5187,49 @@
         <v>0</v>
       </c>
       <c r="R6" s="36"/>
-      <c r="S6" s="36"/>
-      <c r="T6" s="36"/>
-      <c r="U6" s="38">
-        <v>1</v>
-      </c>
-      <c r="V6" s="38">
-        <v>0</v>
-      </c>
-      <c r="W6" s="36"/>
-      <c r="X6" s="39"/>
-      <c r="Y6" s="36"/>
-      <c r="Z6" s="36"/>
-      <c r="AA6" s="36"/>
-      <c r="AB6" s="36"/>
+      <c r="S6" s="36">
+        <v>0</v>
+      </c>
+      <c r="T6" s="36">
+        <v>0</v>
+      </c>
+      <c r="U6" s="50">
+        <v>1</v>
+      </c>
+      <c r="V6" s="50">
+        <v>0</v>
+      </c>
+      <c r="W6" s="36" t="s">
+        <v>455</v>
+      </c>
+      <c r="X6" s="39" t="s">
+        <v>455</v>
+      </c>
+      <c r="Y6" s="36">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="36">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="36">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="36">
+        <v>0</v>
+      </c>
       <c r="AC6" s="36"/>
-      <c r="AD6" s="36"/>
-      <c r="AE6" s="36"/>
-      <c r="AF6" s="38"/>
-      <c r="AG6" s="38"/>
+      <c r="AD6" s="36">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="36">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="50">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="50">
+        <v>0</v>
+      </c>
       <c r="AH6" s="2" t="s">
         <v>477</v>
       </c>
@@ -5248,13 +5268,13 @@
       <c r="G7" s="36">
         <v>6</v>
       </c>
-      <c r="H7" s="38">
-        <v>0.10000000149011599</v>
-      </c>
-      <c r="I7" s="38">
-        <v>0.10000000149011599</v>
-      </c>
-      <c r="J7" s="38">
+      <c r="H7" s="50">
+        <v>0.100000001490116</v>
+      </c>
+      <c r="I7" s="50">
+        <v>0.100000001490116</v>
+      </c>
+      <c r="J7" s="50">
         <v>0.25</v>
       </c>
       <c r="K7" s="36">
@@ -5285,10 +5305,10 @@
       <c r="T7" s="36">
         <v>0</v>
       </c>
-      <c r="U7" s="38">
-        <v>1</v>
-      </c>
-      <c r="V7" s="38">
+      <c r="U7" s="50">
+        <v>1</v>
+      </c>
+      <c r="V7" s="50">
         <v>0</v>
       </c>
       <c r="W7" s="36" t="s">
@@ -5310,16 +5330,18 @@
         <v>1</v>
       </c>
       <c r="AC7" s="36" t="s">
-        <v>480</v>
+        <v>130</v>
       </c>
       <c r="AD7" s="36">
         <v>0</v>
       </c>
-      <c r="AE7" s="36"/>
-      <c r="AF7" s="38">
-        <v>0.6</v>
-      </c>
-      <c r="AG7" s="38">
+      <c r="AE7" s="36">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="50">
+        <v>0.600000023841858</v>
+      </c>
+      <c r="AG7" s="50">
         <v>0</v>
       </c>
       <c r="AH7" s="2" t="s">
@@ -5360,14 +5382,14 @@
       <c r="G8" s="36">
         <v>8</v>
       </c>
-      <c r="H8" s="38">
-        <v>0.10000000149011599</v>
-      </c>
-      <c r="I8" s="38">
+      <c r="H8" s="50">
+        <v>0.100000001490116</v>
+      </c>
+      <c r="I8" s="50">
         <v>0.25</v>
       </c>
-      <c r="J8" s="38">
-        <v>0.10000000149011599</v>
+      <c r="J8" s="50">
+        <v>0.100000001490116</v>
       </c>
       <c r="K8" s="36">
         <v>0</v>
@@ -5397,10 +5419,10 @@
       <c r="T8" s="36">
         <v>0</v>
       </c>
-      <c r="U8" s="38">
-        <v>0.80000001192092896</v>
-      </c>
-      <c r="V8" s="38">
+      <c r="U8" s="50">
+        <v>0.800000011920929</v>
+      </c>
+      <c r="V8" s="50">
         <v>0</v>
       </c>
       <c r="W8" s="36" t="s">
@@ -5428,10 +5450,10 @@
       <c r="AE8" s="36">
         <v>0</v>
       </c>
-      <c r="AF8" s="38">
-        <v>0</v>
-      </c>
-      <c r="AG8" s="38">
+      <c r="AF8" s="50">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="50">
         <v>0</v>
       </c>
       <c r="AH8" s="2" t="s">
@@ -5472,14 +5494,14 @@
       <c r="G9" s="40">
         <v>6</v>
       </c>
-      <c r="H9" s="41">
-        <v>0.20000000298023199</v>
-      </c>
-      <c r="I9" s="41">
-        <v>0.15000000596046401</v>
-      </c>
-      <c r="J9" s="41">
-        <v>0.15000000596046401</v>
+      <c r="H9" s="50">
+        <v>0.200000002980232</v>
+      </c>
+      <c r="I9" s="50">
+        <v>0.150000005960464</v>
+      </c>
+      <c r="J9" s="50">
+        <v>0.150000005960464</v>
       </c>
       <c r="K9" s="40">
         <v>2</v>
@@ -5511,10 +5533,10 @@
       <c r="T9" s="40">
         <v>0</v>
       </c>
-      <c r="U9" s="41">
+      <c r="U9" s="50">
         <v>1.20000004768372</v>
       </c>
-      <c r="V9" s="41">
+      <c r="V9" s="50">
         <v>1</v>
       </c>
       <c r="W9" s="40" t="s">
@@ -5542,10 +5564,10 @@
       <c r="AE9" s="40">
         <v>0</v>
       </c>
-      <c r="AF9" s="41">
-        <v>0</v>
-      </c>
-      <c r="AG9" s="41">
+      <c r="AF9" s="50">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="50">
         <v>0</v>
       </c>
       <c r="AH9" s="26" t="s">
@@ -5581,22 +5603,22 @@
         <v>100</v>
       </c>
       <c r="F10" s="36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G10" s="36">
         <v>6</v>
       </c>
-      <c r="H10" s="38">
+      <c r="H10" s="50">
         <v>0.25</v>
       </c>
-      <c r="I10" s="38">
-        <v>0.20000000298023199</v>
-      </c>
-      <c r="J10" s="38">
-        <v>0.20000000298023199</v>
+      <c r="I10" s="50">
+        <v>0.200000002980232</v>
+      </c>
+      <c r="J10" s="50">
+        <v>0.200000002980232</v>
       </c>
       <c r="K10" s="36">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L10" s="36" t="s">
         <v>484</v>
@@ -5623,10 +5645,10 @@
       <c r="T10" s="36">
         <v>0</v>
       </c>
-      <c r="U10" s="38">
-        <v>1</v>
-      </c>
-      <c r="V10" s="38">
+      <c r="U10" s="50">
+        <v>1</v>
+      </c>
+      <c r="V10" s="50">
         <v>0</v>
       </c>
       <c r="W10" s="36" t="s">
@@ -5656,11 +5678,11 @@
       <c r="AE10" s="36">
         <v>1</v>
       </c>
-      <c r="AF10" s="38">
-        <v>1</v>
-      </c>
-      <c r="AG10" s="38">
-        <v>0.8</v>
+      <c r="AF10" s="50">
+        <v>1</v>
+      </c>
+      <c r="AG10" s="50">
+        <v>0.800000011920929</v>
       </c>
       <c r="AH10" s="2" t="s">
         <v>487</v>
@@ -5675,7 +5697,7 @@
         <v>10</v>
       </c>
       <c r="AL10">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AM10">
         <v>3</v>
@@ -5819,7 +5841,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A705E06-4C8A-43EB-9784-7D906D56BEF6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1:Q45"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
@@ -5839,7 +5861,6 @@
     <col min="14" max="14" width="8.875" style="11" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="10.625" style="11" bestFit="1" customWidth="1"/>
     <col min="16" max="38" width="15.625" style="11" customWidth="1"/>
-    <col min="39" max="16384" width="9" style="11"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17">
@@ -5971,24 +5992,41 @@
         <v>514</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>461</v>
+        <v>417</v>
       </c>
       <c r="E6" s="11">
         <v>1</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>461</v>
+        <v>417</v>
       </c>
       <c r="G6" s="11">
         <v>3</v>
       </c>
       <c r="H6" s="15" t="s">
-        <v>461</v>
+        <v>417</v>
       </c>
       <c r="I6" s="11">
         <v>5</v>
       </c>
-      <c r="J6" s="15"/>
+      <c r="J6" s="15" t="s">
+        <v>455</v>
+      </c>
+      <c r="K6" s="11">
+        <v>0</v>
+      </c>
+      <c r="L6" s="11" t="s">
+        <v>455</v>
+      </c>
+      <c r="M6" s="11">
+        <v>0</v>
+      </c>
+      <c r="N6" s="11" t="s">
+        <v>455</v>
+      </c>
+      <c r="O6" s="11">
+        <v>0</v>
+      </c>
       <c r="P6" s="11">
         <v>1</v>
       </c>
@@ -6004,24 +6042,41 @@
         <v>513</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>543</v>
+        <v>418</v>
       </c>
       <c r="E7" s="11">
         <v>4</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>543</v>
+        <v>418</v>
       </c>
       <c r="G7" s="11">
         <v>5</v>
       </c>
       <c r="H7" s="15" t="s">
-        <v>544</v>
+        <v>419</v>
       </c>
       <c r="I7" s="11">
         <v>2</v>
       </c>
-      <c r="J7" s="15"/>
+      <c r="J7" s="15" t="s">
+        <v>455</v>
+      </c>
+      <c r="K7" s="11">
+        <v>0</v>
+      </c>
+      <c r="L7" s="11" t="s">
+        <v>455</v>
+      </c>
+      <c r="M7" s="11">
+        <v>0</v>
+      </c>
+      <c r="N7" s="11" t="s">
+        <v>455</v>
+      </c>
+      <c r="O7" s="11">
+        <v>0</v>
+      </c>
       <c r="P7" s="11">
         <v>1</v>
       </c>
@@ -6031,35 +6086,47 @@
     </row>
     <row r="8" spans="1:17">
       <c r="B8" s="15" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>548</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>545</v>
+        <v>417</v>
       </c>
       <c r="E8" s="11">
         <v>1</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>461</v>
+        <v>417</v>
       </c>
       <c r="G8" s="11">
         <v>3</v>
       </c>
       <c r="H8" s="15" t="s">
-        <v>546</v>
+        <v>418</v>
       </c>
       <c r="I8" s="11">
         <v>4</v>
       </c>
       <c r="J8" s="11" t="s">
-        <v>544</v>
+        <v>419</v>
       </c>
       <c r="K8" s="11">
         <v>6</v>
       </c>
+      <c r="L8" s="11" t="s">
+        <v>455</v>
+      </c>
+      <c r="M8" s="11">
+        <v>0</v>
+      </c>
+      <c r="N8" s="11" t="s">
+        <v>455</v>
+      </c>
+      <c r="O8" s="11">
+        <v>0</v>
+      </c>
       <c r="P8" s="11">
         <v>1</v>
       </c>
@@ -6069,35 +6136,47 @@
     </row>
     <row r="9" spans="1:17">
       <c r="B9" s="15" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>549</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>461</v>
+        <v>417</v>
       </c>
       <c r="E9" s="11">
         <v>1</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>461</v>
+        <v>417</v>
       </c>
       <c r="G9" s="11">
         <v>3</v>
       </c>
       <c r="H9" s="15" t="s">
-        <v>543</v>
+        <v>418</v>
       </c>
       <c r="I9" s="11">
         <v>5</v>
       </c>
       <c r="J9" s="11" t="s">
-        <v>544</v>
+        <v>419</v>
       </c>
       <c r="K9" s="11">
         <v>2</v>
       </c>
+      <c r="L9" s="11" t="s">
+        <v>455</v>
+      </c>
+      <c r="M9" s="11">
+        <v>0</v>
+      </c>
+      <c r="N9" s="11" t="s">
+        <v>455</v>
+      </c>
+      <c r="O9" s="11">
+        <v>0</v>
+      </c>
       <c r="P9" s="11">
         <v>1</v>
       </c>
@@ -6107,34 +6186,46 @@
     </row>
     <row r="10" spans="1:17">
       <c r="B10" s="15" t="s">
-        <v>515</v>
+        <v>497</v>
       </c>
       <c r="C10" s="15" t="s">
         <v>550</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>543</v>
+        <v>418</v>
       </c>
       <c r="E10" s="11">
         <v>5</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>544</v>
+        <v>419</v>
       </c>
       <c r="G10" s="11">
         <v>1</v>
       </c>
       <c r="H10" s="15" t="s">
-        <v>544</v>
+        <v>419</v>
       </c>
       <c r="I10" s="11">
         <v>2</v>
       </c>
       <c r="J10" s="15" t="s">
-        <v>544</v>
+        <v>419</v>
       </c>
       <c r="K10" s="11">
         <v>3</v>
+      </c>
+      <c r="L10" s="11" t="s">
+        <v>455</v>
+      </c>
+      <c r="M10" s="11">
+        <v>0</v>
+      </c>
+      <c r="N10" s="11" t="s">
+        <v>455</v>
+      </c>
+      <c r="O10" s="11">
+        <v>0</v>
       </c>
       <c r="P10" s="11">
         <v>2</v>
@@ -6151,28 +6242,40 @@
         <v>551</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>543</v>
+        <v>418</v>
       </c>
       <c r="E11" s="11">
         <v>4</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>543</v>
+        <v>418</v>
       </c>
       <c r="G11" s="11">
         <v>6</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>544</v>
+        <v>419</v>
       </c>
       <c r="I11" s="11">
         <v>1</v>
       </c>
       <c r="J11" s="15" t="s">
-        <v>544</v>
+        <v>419</v>
       </c>
       <c r="K11" s="11">
         <v>3</v>
+      </c>
+      <c r="L11" s="11" t="s">
+        <v>455</v>
+      </c>
+      <c r="M11" s="11">
+        <v>0</v>
+      </c>
+      <c r="N11" s="11" t="s">
+        <v>455</v>
+      </c>
+      <c r="O11" s="11">
+        <v>0</v>
       </c>
       <c r="P11" s="11">
         <v>2</v>
@@ -6189,35 +6292,41 @@
         <v>552</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>461</v>
+        <v>417</v>
       </c>
       <c r="E12" s="11">
         <v>1</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>461</v>
+        <v>417</v>
       </c>
       <c r="G12" s="11">
         <v>3</v>
       </c>
       <c r="H12" s="15" t="s">
-        <v>543</v>
+        <v>418</v>
       </c>
       <c r="I12" s="11">
         <v>4</v>
       </c>
       <c r="J12" s="15" t="s">
-        <v>543</v>
+        <v>418</v>
       </c>
       <c r="K12" s="11">
         <v>6</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>544</v>
+        <v>419</v>
       </c>
       <c r="M12" s="11">
         <v>2</v>
       </c>
+      <c r="N12" s="11" t="s">
+        <v>455</v>
+      </c>
+      <c r="O12" s="11">
+        <v>0</v>
+      </c>
       <c r="P12" s="11">
         <v>2</v>
       </c>
@@ -6227,20 +6336,47 @@
     </row>
     <row r="13" spans="1:17">
       <c r="B13" s="43" t="s">
-        <v>553</v>
+        <v>500</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>554</v>
-      </c>
-      <c r="D13" t="s">
-        <v>547</v>
+        <v>559</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>417</v>
       </c>
       <c r="E13" s="11">
         <v>2</v>
       </c>
-      <c r="F13" s="15"/>
-      <c r="H13" s="15"/>
-      <c r="J13" s="15"/>
+      <c r="F13" s="15" t="s">
+        <v>417</v>
+      </c>
+      <c r="G13" s="11">
+        <v>4</v>
+      </c>
+      <c r="H13" s="15" t="s">
+        <v>418</v>
+      </c>
+      <c r="I13" s="11">
+        <v>6</v>
+      </c>
+      <c r="J13" s="15" t="s">
+        <v>419</v>
+      </c>
+      <c r="K13" s="11">
+        <v>1</v>
+      </c>
+      <c r="L13" s="11" t="s">
+        <v>419</v>
+      </c>
+      <c r="M13" s="11">
+        <v>3</v>
+      </c>
+      <c r="N13" s="11" t="s">
+        <v>455</v>
+      </c>
+      <c r="O13" s="11">
+        <v>0</v>
+      </c>
       <c r="P13" s="11">
         <v>4</v>
       </c>
@@ -6250,43 +6386,43 @@
     </row>
     <row r="14" spans="1:17">
       <c r="B14" s="21" t="s">
-        <v>555</v>
+        <v>502</v>
       </c>
       <c r="C14" s="15" t="s">
         <v>556</v>
       </c>
       <c r="D14" s="15" t="s">
-        <v>545</v>
+        <v>417</v>
       </c>
       <c r="E14" s="11">
         <v>1</v>
       </c>
       <c r="F14" s="15" t="s">
-        <v>461</v>
+        <v>417</v>
       </c>
       <c r="G14" s="11">
         <v>3</v>
       </c>
       <c r="H14" s="15" t="s">
-        <v>461</v>
+        <v>417</v>
       </c>
       <c r="I14" s="11">
         <v>4</v>
       </c>
       <c r="J14" s="15" t="s">
-        <v>461</v>
+        <v>417</v>
       </c>
       <c r="K14" s="11">
         <v>6</v>
       </c>
       <c r="L14" s="15" t="s">
-        <v>543</v>
+        <v>418</v>
       </c>
       <c r="M14" s="11">
         <v>5</v>
       </c>
       <c r="N14" s="11" t="s">
-        <v>557</v>
+        <v>419</v>
       </c>
       <c r="O14" s="11">
         <v>2</v>
@@ -6300,40 +6436,46 @@
     </row>
     <row r="15" spans="1:17">
       <c r="B15" s="43" t="s">
-        <v>558</v>
+        <v>501</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>545</v>
+        <v>457</v>
       </c>
       <c r="E15" s="11">
         <v>2</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="G15" s="11">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H15" s="15" t="s">
-        <v>543</v>
+        <v>455</v>
       </c>
       <c r="I15" s="11">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J15" s="15" t="s">
-        <v>544</v>
+        <v>455</v>
       </c>
       <c r="K15" s="11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L15" s="15" t="s">
-        <v>544</v>
+        <v>455</v>
       </c>
       <c r="M15" s="11">
-        <v>3</v>
+        <v>0</v>
+      </c>
+      <c r="N15" s="11" t="s">
+        <v>455</v>
+      </c>
+      <c r="O15" s="11">
+        <v>0</v>
       </c>
       <c r="P15" s="11">
         <v>4</v>
@@ -6344,43 +6486,43 @@
     </row>
     <row r="16" spans="1:17">
       <c r="B16" s="21" t="s">
-        <v>560</v>
+        <v>503</v>
       </c>
       <c r="C16" s="15" t="s">
         <v>561</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>546</v>
+        <v>418</v>
       </c>
       <c r="E16" s="11">
         <v>2</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>543</v>
+        <v>418</v>
       </c>
       <c r="G16" s="11">
         <v>4</v>
       </c>
       <c r="H16" s="15" t="s">
-        <v>543</v>
+        <v>418</v>
       </c>
       <c r="I16" s="11">
         <v>6</v>
       </c>
       <c r="J16" s="15" t="s">
-        <v>544</v>
+        <v>419</v>
       </c>
       <c r="K16" s="11">
         <v>1</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>544</v>
+        <v>419</v>
       </c>
       <c r="M16" s="11">
         <v>3</v>
       </c>
       <c r="N16" s="15" t="s">
-        <v>544</v>
+        <v>419</v>
       </c>
       <c r="O16" s="11">
         <v>5</v>
@@ -6394,43 +6536,47 @@
     </row>
     <row r="17" spans="1:17">
       <c r="B17" s="21" t="s">
-        <v>562</v>
-      </c>
-      <c r="C17" t="s">
+        <v>504</v>
+      </c>
+      <c r="C17" s="11" t="s">
         <v>563</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>545</v>
+        <v>417</v>
       </c>
       <c r="E17" s="11">
         <v>4</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>461</v>
+        <v>417</v>
       </c>
       <c r="G17" s="11">
         <v>6</v>
       </c>
       <c r="H17" s="44" t="s">
-        <v>543</v>
+        <v>418</v>
       </c>
       <c r="I17" s="11">
         <v>5</v>
       </c>
       <c r="J17" s="15" t="s">
-        <v>544</v>
+        <v>419</v>
       </c>
       <c r="K17" s="11">
         <v>1</v>
       </c>
-      <c r="L17" t="s">
-        <v>544</v>
-      </c>
-      <c r="M17">
+      <c r="L17" s="11" t="s">
+        <v>419</v>
+      </c>
+      <c r="M17" s="11">
         <v>3</v>
       </c>
-      <c r="N17"/>
-      <c r="O17"/>
+      <c r="N17" s="11" t="s">
+        <v>455</v>
+      </c>
+      <c r="O17" s="11">
+        <v>0</v>
+      </c>
       <c r="P17" s="11">
         <v>4</v>
       </c>
@@ -6497,10 +6643,10 @@
       </c>
     </row>
     <row r="21" spans="1:17">
-      <c r="B21" t="s">
+      <c r="B21" s="11" t="s">
         <v>417</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="11" t="s">
         <v>490</v>
       </c>
       <c r="E21" s="13">
@@ -6511,10 +6657,10 @@
       </c>
     </row>
     <row r="22" spans="1:17">
-      <c r="B22" t="s">
+      <c r="B22" s="11" t="s">
         <v>418</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="11" t="s">
         <v>421</v>
       </c>
       <c r="E22" s="13">
@@ -6525,10 +6671,10 @@
       </c>
     </row>
     <row r="23" spans="1:17">
-      <c r="B23" t="s">
+      <c r="B23" s="11" t="s">
         <v>419</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="11" t="s">
         <v>422</v>
       </c>
       <c r="E23" s="13">
@@ -6547,10 +6693,10 @@
       </c>
     </row>
     <row r="25" spans="1:17">
-      <c r="B25" t="s">
+      <c r="B25" s="11" t="s">
         <v>457</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="11" t="s">
         <v>458</v>
       </c>
     </row>

--- a/Assets/_ProtoType_Merge/ASB/Data/Excel/H.I 베타 전투 밸런스 데이터 테이블.xlsx
+++ b/Assets/_ProtoType_Merge/ASB/Data/Excel/H.I 베타 전투 밸런스 데이터 테이블.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7615BFD-E49B-4DA8-93B7-038A59603D39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FA11D4D-9365-4CBA-B43D-1CF05F345E2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="801" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="801" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="수정 내역" sheetId="41" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="976" uniqueCount="584">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="979" uniqueCount="587">
   <si>
     <t>Class</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3183,6 +3183,18 @@
       <t>대미지를 준다. 
 단, 부활 효과는 전투당 1회만 적용되며, 이후 사용 시에는 적 전체 공격 효과만 적용된다.</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>V1.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>스킬 설명 수정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>윤태일</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4025,7 +4037,18 @@
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="B19" s="18"/>
+      <c r="A19" t="s">
+        <v>584</v>
+      </c>
+      <c r="B19" s="18">
+        <v>46315</v>
+      </c>
+      <c r="C19" s="30" t="s">
+        <v>585</v>
+      </c>
+      <c r="D19" t="s">
+        <v>586</v>
+      </c>
     </row>
     <row r="20" spans="1:4">
       <c r="B20" s="18"/>
